--- a/Sensitivity_SSIM_Starfish.xlsx
+++ b/Sensitivity_SSIM_Starfish.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\esray\Desktop\comparison_figures\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{58CCB502-DEB7-454C-9403-202E9E08E6E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7994D073-8B2D-4BF0-989B-A64C6B202F3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7DDF5F6B-CF80-492B-B985-49D67CB71709}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6901B53E-FFAE-4076-86C7-9E4395B6FF27}"/>
   </bookViews>
   <sheets>
     <sheet name="Sayfa1" sheetId="1" r:id="rId1"/>
@@ -32,6 +32,9 @@
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="2"/>
     </ext>
   </extLst>
 </workbook>
@@ -442,7 +445,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{670FF004-8610-496B-AFA7-96421C382133}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71744F19-0297-433C-959B-3E325A9CA4CF}">
   <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -576,7 +579,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4FF88598-A665-4C45-967D-CA0DE7EC3D06}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32B3083D-8565-45C8-A1A7-62E63A498C5B}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
@@ -585,7 +588,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8FFDCC9-5026-4EE6-B866-D8F013FE87B3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FA676AA-D398-4117-82CF-4CF100F83A1C}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
